--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -425,7 +425,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.56471476960392</v>
+        <v>36.66011466561532</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.93382364372281</v>
+        <v>33.69948149199701</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48.70346072999317</v>
+        <v>43.56825873739139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input VLCC ($/day)</t>
+          <t>12M TC cycle input Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>61250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip VLCC ($/day)</t>
+          <t>12M FFA strip Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.514704445724115</v>
+        <v>2.49600794144133</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207392.8727342652</v>
+        <v>299841.0477947473</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.698834939905537</v>
+        <v>2.502362041849752</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1132.37</v>
+        <v>942.3718596435604</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1005.36</v>
+        <v>951.940401890348</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1559.202367</v>
+        <v>1315.784628533909</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39.93382364372281</v>
+        <v>33.69948149199701</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.93382364372281</v>
+        <v>33.69948149199701</v>
       </c>
     </row>
     <row r="14">
@@ -771,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot VLCC ($/day)</t>
+          <t>FFA spot Suezmax ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>81500</v>
       </c>
       <c r="C2" t="n">
-        <v>140736.8</v>
+        <v>81500</v>
       </c>
       <c r="D2" t="n">
         <v>3.623488598843554</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>99000</v>
       </c>
       <c r="C3" t="n">
-        <v>172416.8</v>
+        <v>99000</v>
       </c>
       <c r="D3" t="n">
         <v>4.603774728993763</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>92000</v>
       </c>
       <c r="C4" t="n">
-        <v>156576.8</v>
+        <v>92000</v>
       </c>
       <c r="D4" t="n">
         <v>4.153672293359487</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>67500</v>
       </c>
       <c r="C5" t="n">
-        <v>119616.8</v>
+        <v>67500</v>
       </c>
       <c r="D5" t="n">
         <v>2.916577006155644</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="n">
-        <v>109056.8</v>
+        <v>60000</v>
       </c>
       <c r="D6" t="n">
         <v>2.551681029971452</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>78000</v>
       </c>
       <c r="C7" t="n">
-        <v>130176.8</v>
+        <v>78000</v>
       </c>
       <c r="D7" t="n">
         <v>3.350114061381257</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>81500</v>
       </c>
       <c r="C8" t="n">
-        <v>140736.8</v>
+        <v>81500</v>
       </c>
       <c r="D8" t="n">
         <v>3.623488598843554</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="n">
-        <v>103776.8</v>
+        <v>56500</v>
       </c>
       <c r="D9" t="n">
         <v>2.374953131799474</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.34420695995393</v>
+        <v>28.84987874592401</v>
       </c>
       <c r="F11" t="n">
-        <v>27.94740826550541</v>
+        <v>22.81220627290364</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.70346072999317</v>
+        <v>43.56825873739139</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>85000</v>
       </c>
     </row>
   </sheetData>
@@ -1044,7 +1044,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.31526819066326</v>
+        <v>25.59158810747239</v>
       </c>
       <c r="C2" t="n">
-        <v>35.33773865822469</v>
+        <v>30.02359856463496</v>
       </c>
       <c r="D2" t="n">
-        <v>40.36020912578612</v>
+        <v>34.45560902179753</v>
       </c>
       <c r="E2" t="n">
-        <v>45.38267959334755</v>
+        <v>38.8876194789601</v>
       </c>
       <c r="F2" t="n">
-        <v>50.40515006090898</v>
+        <v>43.31962993612267</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.41752101257216</v>
+        <v>26.69384092938129</v>
       </c>
       <c r="C3" t="n">
-        <v>36.43999148013359</v>
+        <v>31.12585138654386</v>
       </c>
       <c r="D3" t="n">
-        <v>41.46246194769502</v>
+        <v>35.55786184370643</v>
       </c>
       <c r="E3" t="n">
-        <v>46.48493241525644</v>
+        <v>39.989872300869</v>
       </c>
       <c r="F3" t="n">
-        <v>51.50740288281788</v>
+        <v>44.42188275803157</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.51977383448106</v>
+        <v>27.79609375129018</v>
       </c>
       <c r="C4" t="n">
-        <v>37.54224430204249</v>
+        <v>32.22810420845276</v>
       </c>
       <c r="D4" t="n">
-        <v>42.56471476960392</v>
+        <v>36.66011466561532</v>
       </c>
       <c r="E4" t="n">
-        <v>47.58718523716534</v>
+        <v>41.09212512277789</v>
       </c>
       <c r="F4" t="n">
-        <v>52.60965570472678</v>
+        <v>45.52413557994046</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.62202665638995</v>
+        <v>28.89834657319908</v>
       </c>
       <c r="C5" t="n">
-        <v>38.64449712395138</v>
+        <v>33.33035703036165</v>
       </c>
       <c r="D5" t="n">
-        <v>43.66696759151281</v>
+        <v>37.76236748752422</v>
       </c>
       <c r="E5" t="n">
-        <v>48.68943805907423</v>
+        <v>42.19437794468679</v>
       </c>
       <c r="F5" t="n">
-        <v>53.71190852663567</v>
+        <v>46.62638840184936</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.72427947829885</v>
+        <v>30.00059939510798</v>
       </c>
       <c r="C6" t="n">
-        <v>39.74674994586028</v>
+        <v>34.43260985227055</v>
       </c>
       <c r="D6" t="n">
-        <v>44.76922041342171</v>
+        <v>38.86462030943312</v>
       </c>
       <c r="E6" t="n">
-        <v>49.79169088098314</v>
+        <v>43.29663076659568</v>
       </c>
       <c r="F6" t="n">
-        <v>54.81416134854457</v>
+        <v>47.72864122375826</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>42.2</v>
+        <v>36.29</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>43.3</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>43.66</v>
+        <v>37.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.66011466561532</v>
+        <v>36.66988066976521</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.69948149199701</v>
+        <v>33.71169501488255</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.56825873739139</v>
+        <v>43.57231386449143</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.49600794144133</v>
+        <v>2.495935317313193</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299841.0477947473</v>
+        <v>299659.8825706947</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.502362041849752</v>
+        <v>2.501033035841905</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>951.940401890348</v>
+        <v>952.4172746777487</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1315.784628533909</v>
+        <v>1316.261501321309</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.69948149199701</v>
+        <v>33.71169501488255</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.69948149199701</v>
+        <v>33.71169501488255</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.84987874592401</v>
+        <v>28.85500713744107</v>
       </c>
       <c r="F11" t="n">
-        <v>22.81220627290364</v>
+        <v>22.81626140000368</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.56825873739139</v>
+        <v>43.57231386449143</v>
       </c>
     </row>
     <row r="13">
@@ -1048,7 +1048,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.59158810747239</v>
+        <v>25.5994009107923</v>
       </c>
       <c r="C2" t="n">
-        <v>30.02359856463496</v>
+        <v>30.03238796836986</v>
       </c>
       <c r="D2" t="n">
-        <v>34.45560902179753</v>
+        <v>34.46537502594742</v>
       </c>
       <c r="E2" t="n">
-        <v>38.8876194789601</v>
+        <v>38.89836208352499</v>
       </c>
       <c r="F2" t="n">
-        <v>43.31962993612267</v>
+        <v>43.33134914110254</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.69384092938129</v>
+        <v>26.7016537327012</v>
       </c>
       <c r="C3" t="n">
-        <v>31.12585138654386</v>
+        <v>31.13464079027876</v>
       </c>
       <c r="D3" t="n">
-        <v>35.55786184370643</v>
+        <v>35.56762784785631</v>
       </c>
       <c r="E3" t="n">
-        <v>39.989872300869</v>
+        <v>40.00061490543388</v>
       </c>
       <c r="F3" t="n">
-        <v>44.42188275803157</v>
+        <v>44.43360196301143</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.79609375129018</v>
+        <v>27.80390655461009</v>
       </c>
       <c r="C4" t="n">
-        <v>32.22810420845276</v>
+        <v>32.23689361218765</v>
       </c>
       <c r="D4" t="n">
-        <v>36.66011466561532</v>
+        <v>36.66988066976521</v>
       </c>
       <c r="E4" t="n">
-        <v>41.09212512277789</v>
+        <v>41.10286772734278</v>
       </c>
       <c r="F4" t="n">
-        <v>45.52413557994046</v>
+        <v>45.53585478492033</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.89834657319908</v>
+        <v>28.90615937651899</v>
       </c>
       <c r="C5" t="n">
-        <v>33.33035703036165</v>
+        <v>33.33914643409655</v>
       </c>
       <c r="D5" t="n">
-        <v>37.76236748752422</v>
+        <v>37.77213349167411</v>
       </c>
       <c r="E5" t="n">
-        <v>42.19437794468679</v>
+        <v>42.20512054925167</v>
       </c>
       <c r="F5" t="n">
-        <v>46.62638840184936</v>
+        <v>46.63810760682922</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.00059939510798</v>
+        <v>30.00841219842789</v>
       </c>
       <c r="C6" t="n">
-        <v>34.43260985227055</v>
+        <v>34.44139925600545</v>
       </c>
       <c r="D6" t="n">
-        <v>38.86462030943312</v>
+        <v>38.874386313583</v>
       </c>
       <c r="E6" t="n">
-        <v>43.29663076659568</v>
+        <v>43.30737337116057</v>
       </c>
       <c r="F6" t="n">
-        <v>47.72864122375826</v>
+        <v>47.74036042873813</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>36.29</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>37.39</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76</v>
+        <v>37.77</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.7</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299659.8825706947</v>
+        <v>324117.2932120436</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.501033035841905</v>
+        <v>2.705160433411495</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.2</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>324117.2932120436</v>
+        <v>346455.0615978089</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.705160433411495</v>
+        <v>2.891596789858387</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.57</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>346455.0615978089</v>
+        <v>333248.0598514805</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.891596789858387</v>
+        <v>2.781367995170809</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.76</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>333248.0598514805</v>
+        <v>377597.4978144598</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.781367995170809</v>
+        <v>3.151519009430332</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.66988066976521</v>
+        <v>36.60167008468765</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.57231386449143</v>
+        <v>43.34494524756623</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>377597.4978144598</v>
+        <v>343848.751885568</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.151519009430332</v>
+        <v>2.869843905768498</v>
       </c>
     </row>
   </sheetData>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.85500713744107</v>
+        <v>28.56746120915828</v>
       </c>
       <c r="F11" t="n">
-        <v>22.81626140000368</v>
+        <v>22.58889278307847</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.57231386449143</v>
+        <v>43.34494524756623</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.5994009107923</v>
+        <v>25.39535227721948</v>
       </c>
       <c r="C2" t="n">
-        <v>30.03238796836986</v>
+        <v>29.72474202837932</v>
       </c>
       <c r="D2" t="n">
-        <v>34.46537502594742</v>
+        <v>34.05413177953916</v>
       </c>
       <c r="E2" t="n">
-        <v>38.89836208352499</v>
+        <v>38.38352153069901</v>
       </c>
       <c r="F2" t="n">
-        <v>43.33134914110254</v>
+        <v>42.71291128185885</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.7016537327012</v>
+        <v>26.66912142979372</v>
       </c>
       <c r="C3" t="n">
-        <v>31.13464079027876</v>
+        <v>30.99851118095356</v>
       </c>
       <c r="D3" t="n">
-        <v>35.56762784785631</v>
+        <v>35.32790093211341</v>
       </c>
       <c r="E3" t="n">
-        <v>40.00061490543388</v>
+        <v>39.65729068327326</v>
       </c>
       <c r="F3" t="n">
-        <v>44.43360196301143</v>
+        <v>43.9866804344331</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.80390655461009</v>
+        <v>27.94289058236796</v>
       </c>
       <c r="C4" t="n">
-        <v>32.23689361218765</v>
+        <v>32.2722803335278</v>
       </c>
       <c r="D4" t="n">
-        <v>36.66988066976521</v>
+        <v>36.60167008468765</v>
       </c>
       <c r="E4" t="n">
-        <v>41.10286772734278</v>
+        <v>40.93105983584751</v>
       </c>
       <c r="F4" t="n">
-        <v>45.53585478492033</v>
+        <v>45.26044958700734</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.90615937651899</v>
+        <v>29.2166597349422</v>
       </c>
       <c r="C5" t="n">
-        <v>33.33914643409655</v>
+        <v>33.54604948610205</v>
       </c>
       <c r="D5" t="n">
-        <v>37.77213349167411</v>
+        <v>37.87543923726189</v>
       </c>
       <c r="E5" t="n">
-        <v>42.20512054925167</v>
+        <v>42.20482898842174</v>
       </c>
       <c r="F5" t="n">
-        <v>46.63810760682922</v>
+        <v>46.53421873958158</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.00841219842789</v>
+        <v>30.49042888751645</v>
       </c>
       <c r="C6" t="n">
-        <v>34.44139925600545</v>
+        <v>34.81981863867629</v>
       </c>
       <c r="D6" t="n">
-        <v>38.874386313583</v>
+        <v>39.14920838983614</v>
       </c>
       <c r="E6" t="n">
-        <v>43.30737337116057</v>
+        <v>43.47859814099599</v>
       </c>
       <c r="F6" t="n">
-        <v>47.74036042873813</v>
+        <v>47.80798789215582</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>36.3</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>37.4</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>37.77</v>
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.60167008468765</v>
+        <v>36.77786581759274</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.71169501488255</v>
+        <v>33.88137310739701</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.34494524756623</v>
+        <v>43.53634880804944</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.495935317313193</v>
+        <v>2.496951204672754</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>343848.751885568</v>
+        <v>341712.0158033373</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.869843905768498</v>
+        <v>2.849094965599591</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>942.3718596435604</v>
+        <v>948.9968822268455</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1316.261501321309</v>
+        <v>1322.886523904594</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.71169501488255</v>
+        <v>33.88137310739701</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.71169501488255</v>
+        <v>33.88137310739701</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.56746120915828</v>
+        <v>28.80952326336817</v>
       </c>
       <c r="F11" t="n">
-        <v>22.58889278307847</v>
+        <v>22.78029634356169</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.34494524756623</v>
+        <v>43.53634880804944</v>
       </c>
     </row>
     <row r="13">
@@ -1047,8 +1047,8 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.39535227721948</v>
+        <v>25.53630886354355</v>
       </c>
       <c r="C2" t="n">
-        <v>29.72474202837932</v>
+        <v>29.8833181879939</v>
       </c>
       <c r="D2" t="n">
-        <v>34.05413177953916</v>
+        <v>34.23032751244425</v>
       </c>
       <c r="E2" t="n">
-        <v>38.38352153069901</v>
+        <v>38.5773368368946</v>
       </c>
       <c r="F2" t="n">
-        <v>42.71291128185885</v>
+        <v>42.92434616134496</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.66912142979372</v>
+        <v>26.81007801611779</v>
       </c>
       <c r="C3" t="n">
-        <v>30.99851118095356</v>
+        <v>31.15708734056814</v>
       </c>
       <c r="D3" t="n">
-        <v>35.32790093211341</v>
+        <v>35.5040966650185</v>
       </c>
       <c r="E3" t="n">
-        <v>39.65729068327326</v>
+        <v>39.85110598946885</v>
       </c>
       <c r="F3" t="n">
-        <v>43.9866804344331</v>
+        <v>44.1981153139192</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.94289058236796</v>
+        <v>28.08384716869203</v>
       </c>
       <c r="C4" t="n">
-        <v>32.2722803335278</v>
+        <v>32.43085649314239</v>
       </c>
       <c r="D4" t="n">
-        <v>36.60167008468765</v>
+        <v>36.77786581759274</v>
       </c>
       <c r="E4" t="n">
-        <v>40.93105983584751</v>
+        <v>41.12487514204309</v>
       </c>
       <c r="F4" t="n">
-        <v>45.26044958700734</v>
+        <v>45.47188446649344</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.2166597349422</v>
+        <v>29.35761632126627</v>
       </c>
       <c r="C5" t="n">
-        <v>33.54604948610205</v>
+        <v>33.70462564571663</v>
       </c>
       <c r="D5" t="n">
-        <v>37.87543923726189</v>
+        <v>38.05163497016698</v>
       </c>
       <c r="E5" t="n">
-        <v>42.20482898842174</v>
+        <v>42.39864429461733</v>
       </c>
       <c r="F5" t="n">
-        <v>46.53421873958158</v>
+        <v>46.74565361906768</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.49042888751645</v>
+        <v>30.63138547384051</v>
       </c>
       <c r="C6" t="n">
-        <v>34.81981863867629</v>
+        <v>34.97839479829086</v>
       </c>
       <c r="D6" t="n">
-        <v>39.14920838983614</v>
+        <v>39.32540412274123</v>
       </c>
       <c r="E6" t="n">
-        <v>43.47859814099599</v>
+        <v>43.67241344719157</v>
       </c>
       <c r="F6" t="n">
-        <v>47.80798789215582</v>
+        <v>48.01942277164193</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>36.56</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>36.69</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>36.73</v>
+        <v>36.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52.48</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341712.0158033373</v>
+        <v>304989.9415076958</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.849094965599591</v>
+        <v>2.542917037509699</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -425,7 +425,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.77786581759274</v>
+        <v>35.40888854514014</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.88137310739701</v>
+        <v>32.16026685098367</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.53634880804944</v>
+        <v>42.98900583150525</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input Suezmax ($/day)</t>
+          <t>12M TC cycle input VLCC ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>111500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip Suezmax ($/day)</t>
+          <t>12M FFA strip VLCC ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.496951204672754</v>
+        <v>2.503573156366993</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>304989.9415076958</v>
+        <v>326486.1458949595</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.542917037509699</v>
+        <v>2.704128816310348</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>948.9968822268455</v>
+        <v>936.3968822268454</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>952.4172746777487</v>
+        <v>897.8172746777486</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1322.886523904594</v>
+        <v>1255.686523904594</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33.88137310739701</v>
+        <v>32.16026685098367</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.88137310739701</v>
+        <v>32.16026685098367</v>
       </c>
     </row>
     <row r="14">
@@ -771,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot Suezmax ($/day)</t>
+          <t>FFA spot VLCC ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>147500</v>
       </c>
       <c r="C2" t="n">
-        <v>81500</v>
+        <v>140736.8</v>
       </c>
       <c r="D2" t="n">
         <v>3.623488598843554</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>183500</v>
       </c>
       <c r="C3" t="n">
-        <v>99000</v>
+        <v>172416.8</v>
       </c>
       <c r="D3" t="n">
         <v>4.603774728993763</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>165500</v>
       </c>
       <c r="C4" t="n">
-        <v>92000</v>
+        <v>156576.8</v>
       </c>
       <c r="D4" t="n">
         <v>4.153672293359487</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>123500</v>
       </c>
       <c r="C5" t="n">
-        <v>67500</v>
+        <v>119616.8</v>
       </c>
       <c r="D5" t="n">
         <v>2.916577006155644</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>111500</v>
       </c>
       <c r="C6" t="n">
-        <v>60000</v>
+        <v>109056.8</v>
       </c>
       <c r="D6" t="n">
         <v>2.551681029971452</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>135500</v>
       </c>
       <c r="C7" t="n">
-        <v>78000</v>
+        <v>130176.8</v>
       </c>
       <c r="D7" t="n">
         <v>3.350114061381257</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>147500</v>
       </c>
       <c r="C8" t="n">
-        <v>81500</v>
+        <v>140736.8</v>
       </c>
       <c r="D8" t="n">
         <v>3.623488598843554</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>105500</v>
       </c>
       <c r="C9" t="n">
-        <v>56500</v>
+        <v>103776.8</v>
       </c>
       <c r="D9" t="n">
         <v>2.374953131799474</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.80952326336817</v>
+        <v>28.11731584086693</v>
       </c>
       <c r="F11" t="n">
-        <v>22.78029634356169</v>
+        <v>22.23295336701749</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.53634880804944</v>
+        <v>42.98900583150525</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>155000</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1048,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.53630886354355</v>
+        <v>24.44112704558147</v>
       </c>
       <c r="C2" t="n">
-        <v>29.8833181879939</v>
+        <v>28.65123864278656</v>
       </c>
       <c r="D2" t="n">
-        <v>34.23032751244425</v>
+        <v>32.86135023999166</v>
       </c>
       <c r="E2" t="n">
-        <v>38.5773368368946</v>
+        <v>37.07146183719676</v>
       </c>
       <c r="F2" t="n">
-        <v>42.92434616134496</v>
+        <v>41.28157343440185</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.81007801611779</v>
+        <v>25.71489619815572</v>
       </c>
       <c r="C3" t="n">
-        <v>31.15708734056814</v>
+        <v>29.92500779536081</v>
       </c>
       <c r="D3" t="n">
-        <v>35.5040966650185</v>
+        <v>34.1351193925659</v>
       </c>
       <c r="E3" t="n">
-        <v>39.85110598946885</v>
+        <v>38.345230989771</v>
       </c>
       <c r="F3" t="n">
-        <v>44.1981153139192</v>
+        <v>42.5553425869761</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.08384716869203</v>
+        <v>26.98866535072996</v>
       </c>
       <c r="C4" t="n">
-        <v>32.43085649314239</v>
+        <v>31.19877694793505</v>
       </c>
       <c r="D4" t="n">
-        <v>36.77786581759274</v>
+        <v>35.40888854514014</v>
       </c>
       <c r="E4" t="n">
-        <v>41.12487514204309</v>
+        <v>39.61900014234524</v>
       </c>
       <c r="F4" t="n">
-        <v>45.47188446649344</v>
+        <v>43.82911173955033</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.35761632126627</v>
+        <v>28.2624345033042</v>
       </c>
       <c r="C5" t="n">
-        <v>33.70462564571663</v>
+        <v>32.47254610050929</v>
       </c>
       <c r="D5" t="n">
-        <v>38.05163497016698</v>
+        <v>36.68265769771438</v>
       </c>
       <c r="E5" t="n">
-        <v>42.39864429461733</v>
+        <v>40.89276929491948</v>
       </c>
       <c r="F5" t="n">
-        <v>46.74565361906768</v>
+        <v>45.10288089212457</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.63138547384051</v>
+        <v>29.53620365587845</v>
       </c>
       <c r="C6" t="n">
-        <v>34.97839479829086</v>
+        <v>33.74631525308354</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32540412274123</v>
+        <v>37.95642685028863</v>
       </c>
       <c r="E6" t="n">
-        <v>43.67241344719157</v>
+        <v>42.16653844749372</v>
       </c>
       <c r="F6" t="n">
-        <v>48.01942277164193</v>
+        <v>46.37665004469882</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>36.73</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>36.87</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>36.91</v>
+        <v>35.54</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -425,7 +425,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.88</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.40888854514014</v>
+        <v>37.33182097764502</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.16026685098367</v>
+        <v>34.55905869585976</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42.98900583150525</v>
+        <v>43.80159963514394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input VLCC ($/day)</t>
+          <t>12M TC cycle input Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>61250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip VLCC ($/day)</t>
+          <t>12M FFA strip Suezmax ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.503573156366993</v>
+        <v>2.492977754612666</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>326486.1458949595</v>
+        <v>292039.0015738553</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.704128816310348</v>
+        <v>2.444709859423283</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>936.3968822268454</v>
+        <v>948.9968822268455</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.8172746777486</v>
+        <v>978.8772746777487</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1255.686523904594</v>
+        <v>1349.346523904594</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.16026685098367</v>
+        <v>34.55905869585976</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.16026685098367</v>
+        <v>34.55905869585976</v>
       </c>
     </row>
     <row r="14">
@@ -771,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot VLCC ($/day)</t>
+          <t>FFA spot Suezmax ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>81500</v>
       </c>
       <c r="C2" t="n">
-        <v>140736.8</v>
+        <v>81500</v>
       </c>
       <c r="D2" t="n">
         <v>3.623488598843554</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>99000</v>
       </c>
       <c r="C3" t="n">
-        <v>172416.8</v>
+        <v>99000</v>
       </c>
       <c r="D3" t="n">
         <v>4.603774728993763</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>92000</v>
       </c>
       <c r="C4" t="n">
-        <v>156576.8</v>
+        <v>92000</v>
       </c>
       <c r="D4" t="n">
         <v>4.153672293359487</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>67500</v>
       </c>
       <c r="C5" t="n">
-        <v>119616.8</v>
+        <v>67500</v>
       </c>
       <c r="D5" t="n">
         <v>2.916577006155644</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>60000</v>
       </c>
       <c r="C6" t="n">
-        <v>109056.8</v>
+        <v>60000</v>
       </c>
       <c r="D6" t="n">
         <v>2.551681029971452</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>78000</v>
       </c>
       <c r="C7" t="n">
-        <v>130176.8</v>
+        <v>78000</v>
       </c>
       <c r="D7" t="n">
         <v>3.350114061381257</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>81500</v>
       </c>
       <c r="C8" t="n">
-        <v>140736.8</v>
+        <v>81500</v>
       </c>
       <c r="D8" t="n">
         <v>3.623488598843554</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="n">
-        <v>103776.8</v>
+        <v>56500</v>
       </c>
       <c r="D9" t="n">
         <v>2.374953131799474</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.11731584086693</v>
+        <v>29.14497762965723</v>
       </c>
       <c r="F11" t="n">
-        <v>22.23295336701749</v>
+        <v>23.04554717065618</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>42.98900583150525</v>
+        <v>43.80159963514394</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>85000</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1047,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.44112704558147</v>
+        <v>25.97947299158536</v>
       </c>
       <c r="C2" t="n">
-        <v>28.65123864278656</v>
+        <v>30.38187783204094</v>
       </c>
       <c r="D2" t="n">
-        <v>32.86135023999166</v>
+        <v>34.78428267249653</v>
       </c>
       <c r="E2" t="n">
-        <v>37.07146183719676</v>
+        <v>39.1866875129521</v>
       </c>
       <c r="F2" t="n">
-        <v>41.28157343440185</v>
+        <v>43.58909235340769</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.71489619815572</v>
+        <v>27.2532421441596</v>
       </c>
       <c r="C3" t="n">
-        <v>29.92500779536081</v>
+        <v>31.65564698461519</v>
       </c>
       <c r="D3" t="n">
-        <v>34.1351193925659</v>
+        <v>36.05805182507077</v>
       </c>
       <c r="E3" t="n">
-        <v>38.345230989771</v>
+        <v>40.46045666552635</v>
       </c>
       <c r="F3" t="n">
-        <v>42.5553425869761</v>
+        <v>44.86286150598193</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.98866535072996</v>
+        <v>28.52701129673385</v>
       </c>
       <c r="C4" t="n">
-        <v>31.19877694793505</v>
+        <v>32.92941613718943</v>
       </c>
       <c r="D4" t="n">
-        <v>35.40888854514014</v>
+        <v>37.33182097764502</v>
       </c>
       <c r="E4" t="n">
-        <v>39.61900014234524</v>
+        <v>41.73422581810059</v>
       </c>
       <c r="F4" t="n">
-        <v>43.82911173955033</v>
+        <v>46.13663065855617</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.2624345033042</v>
+        <v>29.80078044930809</v>
       </c>
       <c r="C5" t="n">
-        <v>32.47254610050929</v>
+        <v>34.20318528976367</v>
       </c>
       <c r="D5" t="n">
-        <v>36.68265769771438</v>
+        <v>38.60559013021926</v>
       </c>
       <c r="E5" t="n">
-        <v>40.89276929491948</v>
+        <v>43.00799497067483</v>
       </c>
       <c r="F5" t="n">
-        <v>45.10288089212457</v>
+        <v>47.4103998111304</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.53620365587845</v>
+        <v>31.07454960188233</v>
       </c>
       <c r="C6" t="n">
-        <v>33.74631525308354</v>
+        <v>35.47695444233791</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95642685028863</v>
+        <v>39.8793592827935</v>
       </c>
       <c r="E6" t="n">
-        <v>42.16653844749372</v>
+        <v>44.28176412324908</v>
       </c>
       <c r="F6" t="n">
-        <v>46.37665004469882</v>
+        <v>48.68416896370465</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>35.37</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>35.5</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54</v>
+        <v>37.46</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.6</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>292039.0015738553</v>
+        <v>299354.0533849047</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.444709859423283</v>
+        <v>2.505945445041261</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.33182097764502</v>
+        <v>37.18391296596901</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.55905869585976</v>
+        <v>34.35233718422831</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.80159963514394</v>
+        <v>43.79092312336398</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.492977754612666</v>
+        <v>2.493422768490981</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299354.0533849047</v>
+        <v>301800.2921685451</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.505945445041261</v>
+        <v>2.523363202180821</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>978.8772746777487</v>
+        <v>970.8059045750206</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1349.346523904594</v>
+        <v>1341.275153801866</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55905869585976</v>
+        <v>34.35233718422831</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.55905869585976</v>
+        <v>34.35233718422831</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29.14497762965723</v>
+        <v>29.13147538149252</v>
       </c>
       <c r="F11" t="n">
-        <v>23.04554717065618</v>
+        <v>23.03487065887622</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.80159963514394</v>
+        <v>43.79092312336398</v>
       </c>
     </row>
     <row r="13">
@@ -1048,7 +1048,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.97947299158536</v>
+        <v>25.86114658224457</v>
       </c>
       <c r="C2" t="n">
-        <v>30.38187783204094</v>
+        <v>30.24876062153254</v>
       </c>
       <c r="D2" t="n">
-        <v>34.78428267249653</v>
+        <v>34.63637466082052</v>
       </c>
       <c r="E2" t="n">
-        <v>39.1866875129521</v>
+        <v>39.0239887001085</v>
       </c>
       <c r="F2" t="n">
-        <v>43.58909235340769</v>
+        <v>43.41160273939647</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.2532421441596</v>
+        <v>27.13491573481881</v>
       </c>
       <c r="C3" t="n">
-        <v>31.65564698461519</v>
+        <v>31.52252977410679</v>
       </c>
       <c r="D3" t="n">
-        <v>36.05805182507077</v>
+        <v>35.91014381339477</v>
       </c>
       <c r="E3" t="n">
-        <v>40.46045666552635</v>
+        <v>40.29775785268275</v>
       </c>
       <c r="F3" t="n">
-        <v>44.86286150598193</v>
+        <v>44.68537189197072</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.52701129673385</v>
+        <v>28.40868488739305</v>
       </c>
       <c r="C4" t="n">
-        <v>32.92941613718943</v>
+        <v>32.79629892668103</v>
       </c>
       <c r="D4" t="n">
-        <v>37.33182097764502</v>
+        <v>37.18391296596901</v>
       </c>
       <c r="E4" t="n">
-        <v>41.73422581810059</v>
+        <v>41.57152700525699</v>
       </c>
       <c r="F4" t="n">
-        <v>46.13663065855617</v>
+        <v>45.95914104454496</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.80078044930809</v>
+        <v>29.68245403996729</v>
       </c>
       <c r="C5" t="n">
-        <v>34.20318528976367</v>
+        <v>34.07006807925526</v>
       </c>
       <c r="D5" t="n">
-        <v>38.60559013021926</v>
+        <v>38.45768211854325</v>
       </c>
       <c r="E5" t="n">
-        <v>43.00799497067483</v>
+        <v>42.84529615783123</v>
       </c>
       <c r="F5" t="n">
-        <v>47.4103998111304</v>
+        <v>47.2329101971192</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.07454960188233</v>
+        <v>30.95622319254154</v>
       </c>
       <c r="C6" t="n">
-        <v>35.47695444233791</v>
+        <v>35.34383723182951</v>
       </c>
       <c r="D6" t="n">
-        <v>39.8793592827935</v>
+        <v>39.73145127111749</v>
       </c>
       <c r="E6" t="n">
-        <v>44.28176412324908</v>
+        <v>44.11906531040547</v>
       </c>
       <c r="F6" t="n">
-        <v>48.68416896370465</v>
+        <v>48.50667934969344</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>37.29</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>37.42</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>37.46</v>
+        <v>37.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.12</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>301800.2921685451</v>
+        <v>299265.0880755464</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.523363202180821</v>
+        <v>2.502166268697674</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -1274,7 +1274,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.94</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299265.0880755464</v>
+        <v>343912.849046688</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.502166268697674</v>
+        <v>2.875467819484197</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.11</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>343912.849046688</v>
+        <v>331518.5179253617</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.875467819484197</v>
+        <v>2.771838366899926</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52.23</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>331518.5179253617</v>
+        <v>369687.4239921736</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.771838366899926</v>
+        <v>3.090969976562853</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.94</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>369687.4239921736</v>
+        <v>359264.9182765127</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.090969976562853</v>
+        <v>3.003827027798806</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.2</v>
+        <v>56.73</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>359264.9182765127</v>
+        <v>394898.6202503261</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.003827027798806</v>
+        <v>3.301761703978587</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.73</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>394898.6202503261</v>
+        <v>354757.8887778487</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.301761703978587</v>
+        <v>2.966143590495435</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.18391296596901</v>
+        <v>37.19451650209299</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.35233718422831</v>
+        <v>34.42282296047961</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.79092312336398</v>
+        <v>43.66180143252423</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.493422768490981</v>
+        <v>2.491368819822664</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>354757.8887778487</v>
+        <v>353871.3179144677</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.966143590495435</v>
+        <v>2.964894910218178</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>948.9968822268455</v>
+        <v>943.5280646247628</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>970.8059045750206</v>
+        <v>979.0268149932425</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1341.275153801866</v>
+        <v>1344.027246618005</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.35233718422831</v>
+        <v>34.42282296047961</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.35233718422831</v>
+        <v>34.42282296047961</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29.13147538149252</v>
+        <v>28.96817924609767</v>
       </c>
       <c r="F11" t="n">
-        <v>23.03487065887622</v>
+        <v>22.90574896803648</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.79092312336398</v>
+        <v>43.66180143252423</v>
       </c>
     </row>
     <row r="13">
@@ -1048,7 +1048,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.86114658224457</v>
+        <v>25.86962941114375</v>
       </c>
       <c r="C2" t="n">
-        <v>30.24876062153254</v>
+        <v>30.25830380404413</v>
       </c>
       <c r="D2" t="n">
-        <v>34.63637466082052</v>
+        <v>34.64697819694451</v>
       </c>
       <c r="E2" t="n">
-        <v>39.0239887001085</v>
+        <v>39.03565258984489</v>
       </c>
       <c r="F2" t="n">
-        <v>43.41160273939647</v>
+        <v>43.42432698274527</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.13491573481881</v>
+        <v>27.143398563718</v>
       </c>
       <c r="C3" t="n">
-        <v>31.52252977410679</v>
+        <v>31.53207295661838</v>
       </c>
       <c r="D3" t="n">
-        <v>35.91014381339477</v>
+        <v>35.92074734951876</v>
       </c>
       <c r="E3" t="n">
-        <v>40.29775785268275</v>
+        <v>40.30942174241914</v>
       </c>
       <c r="F3" t="n">
-        <v>44.68537189197072</v>
+        <v>44.69809613531952</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.40868488739305</v>
+        <v>28.41716771629224</v>
       </c>
       <c r="C4" t="n">
-        <v>32.79629892668103</v>
+        <v>32.80584210919262</v>
       </c>
       <c r="D4" t="n">
-        <v>37.18391296596901</v>
+        <v>37.19451650209299</v>
       </c>
       <c r="E4" t="n">
-        <v>41.57152700525699</v>
+        <v>41.58319089499338</v>
       </c>
       <c r="F4" t="n">
-        <v>45.95914104454496</v>
+        <v>45.97186528789376</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.68245403996729</v>
+        <v>29.69093686886648</v>
       </c>
       <c r="C5" t="n">
-        <v>34.07006807925526</v>
+        <v>34.07961126176686</v>
       </c>
       <c r="D5" t="n">
-        <v>38.45768211854325</v>
+        <v>38.46828565466723</v>
       </c>
       <c r="E5" t="n">
-        <v>42.84529615783123</v>
+        <v>42.85696004756763</v>
       </c>
       <c r="F5" t="n">
-        <v>47.2329101971192</v>
+        <v>47.245634440468</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.95622319254154</v>
+        <v>30.96470602144073</v>
       </c>
       <c r="C6" t="n">
-        <v>35.34383723182951</v>
+        <v>35.3533804143411</v>
       </c>
       <c r="D6" t="n">
-        <v>39.73145127111749</v>
+        <v>39.74205480724148</v>
       </c>
       <c r="E6" t="n">
-        <v>44.11906531040547</v>
+        <v>44.13072920014187</v>
       </c>
       <c r="F6" t="n">
-        <v>48.50667934969344</v>
+        <v>48.51940359304224</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>37.14</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>37.27</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>37.32</v>
+        <v>37.33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.88</v>
+        <v>54.24</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>353871.3179144677</v>
+        <v>358931.1847998503</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.964894910218178</v>
+        <v>3.007288777184471</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54.24</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>358931.1847998503</v>
+        <v>410092.0610853866</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.007288777184471</v>
+        <v>3.435937876510321</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57.88</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>410092.0610853866</v>
+        <v>446635.5441464838</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.435937876510321</v>
+        <v>3.742115804600213</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.48</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>446635.5441464838</v>
+        <v>466031.7005404506</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.742115804600213</v>
+        <v>3.904625627971002</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.19451650209299</v>
+        <v>40.24200852246209</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.42282296047961</v>
+        <v>37.64884389070714</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43.66180143252423</v>
+        <v>46.29272599655697</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.491368819822664</v>
+        <v>2.489012218774916</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>466031.7005404506</v>
+        <v>421885.9753859958</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.904625627971002</v>
+        <v>3.545750707714429</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>943.5280646247628</v>
+        <v>915.4306703049403</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>979.0268149932425</v>
+        <v>970.1923305565776</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>176.519699</v>
+        <v>247.806903</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.90000000000001</v>
+        <v>138.45</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-683.0873319999999</v>
+        <v>-722.493783</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-158.86</v>
+        <v>-79.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1344.027246618005</v>
+        <v>1469.986120861518</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.42282296047961</v>
+        <v>37.64884389070714</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.42282296047961</v>
+        <v>37.64884389070714</v>
       </c>
     </row>
     <row r="14">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.96817924609767</v>
+        <v>32.29542667468917</v>
       </c>
       <c r="F11" t="n">
-        <v>22.90574896803648</v>
+        <v>25.53667353206922</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.66180143252423</v>
+        <v>46.29272599655697</v>
       </c>
     </row>
     <row r="13">
@@ -1047,7 +1047,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.86962941114375</v>
+        <v>29.08961928805215</v>
       </c>
       <c r="C2" t="n">
-        <v>30.25830380404413</v>
+        <v>33.39204475268287</v>
       </c>
       <c r="D2" t="n">
-        <v>34.64697819694451</v>
+        <v>37.69447021731361</v>
       </c>
       <c r="E2" t="n">
-        <v>39.03565258984489</v>
+        <v>41.99689568194434</v>
       </c>
       <c r="F2" t="n">
-        <v>43.42432698274527</v>
+        <v>46.29932114657506</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.143398563718</v>
+        <v>30.36338844062639</v>
       </c>
       <c r="C3" t="n">
-        <v>31.53207295661838</v>
+        <v>34.66581390525712</v>
       </c>
       <c r="D3" t="n">
-        <v>35.92074734951876</v>
+        <v>38.96823936988785</v>
       </c>
       <c r="E3" t="n">
-        <v>40.30942174241914</v>
+        <v>43.27066483451858</v>
       </c>
       <c r="F3" t="n">
-        <v>44.69809613531952</v>
+        <v>47.57309029914931</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.41716771629224</v>
+        <v>31.63715759320063</v>
       </c>
       <c r="C4" t="n">
-        <v>32.80584210919262</v>
+        <v>35.93958305783136</v>
       </c>
       <c r="D4" t="n">
-        <v>37.19451650209299</v>
+        <v>40.24200852246209</v>
       </c>
       <c r="E4" t="n">
-        <v>41.58319089499338</v>
+        <v>44.54443398709282</v>
       </c>
       <c r="F4" t="n">
-        <v>45.97186528789376</v>
+        <v>48.84685945172355</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.69093686886648</v>
+        <v>32.91092674577487</v>
       </c>
       <c r="C5" t="n">
-        <v>34.07961126176686</v>
+        <v>37.2133522104056</v>
       </c>
       <c r="D5" t="n">
-        <v>38.46828565466723</v>
+        <v>41.51577767503633</v>
       </c>
       <c r="E5" t="n">
-        <v>42.85696004756763</v>
+        <v>45.81820313966706</v>
       </c>
       <c r="F5" t="n">
-        <v>47.245634440468</v>
+        <v>50.12062860429779</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.96470602144073</v>
+        <v>34.18469589834912</v>
       </c>
       <c r="C6" t="n">
-        <v>35.3533804143411</v>
+        <v>38.48712136297984</v>
       </c>
       <c r="D6" t="n">
-        <v>39.74205480724148</v>
+        <v>42.78954682761058</v>
       </c>
       <c r="E6" t="n">
-        <v>44.13072920014187</v>
+        <v>47.09197229224131</v>
       </c>
       <c r="F6" t="n">
-        <v>48.51940359304224</v>
+        <v>51.39439775687203</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>37.15</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>37.28</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>37.33</v>
+        <v>40.37</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -425,7 +425,7 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40.24200852246209</v>
+        <v>42.03250518583511</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.64884389070714</v>
+        <v>39.5374388450766</v>
       </c>
     </row>
     <row r="8">
@@ -512,27 +512,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.29272599655697</v>
+        <v>47.85432664760496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>12M TC cycle input Suezmax ($/day)</t>
+          <t>12M TC cycle input VLCC ($/day)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>111500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12M FFA strip Suezmax ($/day)</t>
+          <t>12M FFA strip VLCC ($/day)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.489012218774916</v>
+        <v>2.500244190919798</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>421885.9753859958</v>
+        <v>401318.5935331045</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.545750707714429</v>
+        <v>3.334900492851576</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>915.4306703049403</v>
+        <v>989.1702087330365</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1469.986120861518</v>
+        <v>1543.725659289614</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37.64884389070714</v>
+        <v>39.5374388450766</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.64884389070714</v>
+        <v>39.5374388450766</v>
       </c>
     </row>
     <row r="14">
@@ -771,7 +771,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FFA spot Suezmax ($/day)</t>
+          <t>FFA spot VLCC ($/day)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>147500</v>
       </c>
       <c r="C2" t="n">
-        <v>81500</v>
+        <v>140736.8</v>
       </c>
       <c r="D2" t="n">
         <v>3.623488598843554</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>183500</v>
       </c>
       <c r="C3" t="n">
-        <v>99000</v>
+        <v>172416.8</v>
       </c>
       <c r="D3" t="n">
         <v>4.603774728993763</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>165500</v>
       </c>
       <c r="C4" t="n">
-        <v>92000</v>
+        <v>156576.8</v>
       </c>
       <c r="D4" t="n">
         <v>4.153672293359487</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>123500</v>
       </c>
       <c r="C5" t="n">
-        <v>67500</v>
+        <v>119616.8</v>
       </c>
       <c r="D5" t="n">
         <v>2.916577006155644</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>111500</v>
       </c>
       <c r="C6" t="n">
-        <v>60000</v>
+        <v>109056.8</v>
       </c>
       <c r="D6" t="n">
         <v>2.551681029971452</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>135500</v>
       </c>
       <c r="C7" t="n">
-        <v>78000</v>
+        <v>130176.8</v>
       </c>
       <c r="D7" t="n">
         <v>3.350114061381257</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>147500</v>
       </c>
       <c r="C8" t="n">
-        <v>81500</v>
+        <v>140736.8</v>
       </c>
       <c r="D8" t="n">
         <v>3.623488598843554</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>105500</v>
       </c>
       <c r="C9" t="n">
-        <v>56500</v>
+        <v>103776.8</v>
       </c>
       <c r="D9" t="n">
         <v>2.374953131799474</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32.29542667468917</v>
+        <v>34.27033383155648</v>
       </c>
       <c r="F11" t="n">
-        <v>25.53667353206922</v>
+        <v>27.09827418311721</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>46.29272599655697</v>
+        <v>47.85432664760496</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>155000</v>
       </c>
     </row>
   </sheetData>
@@ -1047,7 +1047,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.08961928805215</v>
+        <v>30.52201661875056</v>
       </c>
       <c r="C2" t="n">
-        <v>33.39204475268287</v>
+        <v>35.00349174971859</v>
       </c>
       <c r="D2" t="n">
-        <v>37.69447021731361</v>
+        <v>39.48496688068662</v>
       </c>
       <c r="E2" t="n">
-        <v>41.99689568194434</v>
+        <v>43.96644201165465</v>
       </c>
       <c r="F2" t="n">
-        <v>46.29932114657506</v>
+        <v>48.44791714262269</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.36338844062639</v>
+        <v>31.79578577132481</v>
       </c>
       <c r="C3" t="n">
-        <v>34.66581390525712</v>
+        <v>36.27726090229283</v>
       </c>
       <c r="D3" t="n">
-        <v>38.96823936988785</v>
+        <v>40.75873603326087</v>
       </c>
       <c r="E3" t="n">
-        <v>43.27066483451858</v>
+        <v>45.2402111642289</v>
       </c>
       <c r="F3" t="n">
-        <v>47.57309029914931</v>
+        <v>49.72168629519692</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.63715759320063</v>
+        <v>33.06955492389905</v>
       </c>
       <c r="C4" t="n">
-        <v>35.93958305783136</v>
+        <v>37.55103005486708</v>
       </c>
       <c r="D4" t="n">
-        <v>40.24200852246209</v>
+        <v>42.03250518583511</v>
       </c>
       <c r="E4" t="n">
-        <v>44.54443398709282</v>
+        <v>46.51398031680313</v>
       </c>
       <c r="F4" t="n">
-        <v>48.84685945172355</v>
+        <v>50.99545544777116</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.91092674577487</v>
+        <v>34.34332407647329</v>
       </c>
       <c r="C5" t="n">
-        <v>37.2133522104056</v>
+        <v>38.82479920744132</v>
       </c>
       <c r="D5" t="n">
-        <v>41.51577767503633</v>
+        <v>43.30627433840935</v>
       </c>
       <c r="E5" t="n">
-        <v>45.81820313966706</v>
+        <v>47.78774946937737</v>
       </c>
       <c r="F5" t="n">
-        <v>50.12062860429779</v>
+        <v>52.26922460034541</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.18469589834912</v>
+        <v>35.61709322904753</v>
       </c>
       <c r="C6" t="n">
-        <v>38.48712136297984</v>
+        <v>40.09856836001556</v>
       </c>
       <c r="D6" t="n">
-        <v>42.78954682761058</v>
+        <v>44.5800434909836</v>
       </c>
       <c r="E6" t="n">
-        <v>47.09197229224131</v>
+        <v>49.06151862195162</v>
       </c>
       <c r="F6" t="n">
-        <v>51.39439775687203</v>
+        <v>53.54299375291966</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>40.2</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>40.33</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>40.37</v>
+        <v>42.16</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.03250518583511</v>
+        <v>39.72900256646593</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.85432664760496</v>
+        <v>40.17598458304104</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>105700</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.500244190919798</v>
+        <v>2.369938537385169</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401318.5935331045</v>
+        <v>530103.5142182048</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.334900492851576</v>
+        <v>4.576269250885495</v>
       </c>
     </row>
   </sheetData>
@@ -773,8 +773,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>140736.8</v>
+        <v>169028.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.623488598843554</v>
+        <v>4.997078959757232</v>
       </c>
       <c r="E2" t="n">
-        <v>3.079965309017021</v>
+        <v>4.247517115793647</v>
       </c>
       <c r="F2" t="n">
-        <v>3.000648193365846</v>
+        <v>4.138132505091238</v>
       </c>
     </row>
     <row r="3">
@@ -839,19 +839,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>172416.8</v>
+        <v>169028.8</v>
       </c>
       <c r="D3" t="n">
-        <v>4.603774728993763</v>
+        <v>4.997078959757232</v>
       </c>
       <c r="E3" t="n">
-        <v>3.913208519644698</v>
+        <v>4.247517115793647</v>
       </c>
       <c r="F3" t="n">
-        <v>3.714253155467566</v>
+        <v>4.031564832551133</v>
       </c>
     </row>
     <row r="4">
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>156576.8</v>
+        <v>103952.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4.153672293359487</v>
+        <v>2.413639243947219</v>
       </c>
       <c r="E4" t="n">
-        <v>3.530621449355564</v>
+        <v>2.051593357355136</v>
       </c>
       <c r="F4" t="n">
-        <v>3.264817586950424</v>
+        <v>1.897138554909731</v>
       </c>
     </row>
     <row r="5">
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>119616.8</v>
+        <v>103952.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.916577006155644</v>
+        <v>2.413639243947219</v>
       </c>
       <c r="E5" t="n">
-        <v>2.479090455232297</v>
+        <v>2.051593357355136</v>
       </c>
       <c r="F5" t="n">
-        <v>2.233414824533601</v>
+        <v>1.848282303923546</v>
       </c>
     </row>
     <row r="6">
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>109056.8</v>
+        <v>53924.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2.551681029971452</v>
+        <v>0.786333150608707</v>
       </c>
       <c r="E6" t="n">
-        <v>2.168928875475734</v>
+        <v>0.668383178017401</v>
       </c>
       <c r="F6" t="n">
-        <v>1.903669654944936</v>
+        <v>0.5866401560024881</v>
       </c>
     </row>
     <row r="7">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>130176.8</v>
+        <v>53924.8</v>
       </c>
       <c r="D7" t="n">
-        <v>3.350114061381257</v>
+        <v>0.786333150608707</v>
       </c>
       <c r="E7" t="n">
-        <v>2.847596952174068</v>
+        <v>0.668383178017401</v>
       </c>
       <c r="F7" t="n">
-        <v>2.434972446699516</v>
+        <v>0.5715326465240378</v>
       </c>
     </row>
     <row r="8">
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>140736.8</v>
+        <v>53924.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3.623488598843554</v>
+        <v>0.786333150608707</v>
       </c>
       <c r="E8" t="n">
-        <v>3.079965309017021</v>
+        <v>0.668383178017401</v>
       </c>
       <c r="F8" t="n">
-        <v>2.56584614880494</v>
+        <v>0.556814194699255</v>
       </c>
     </row>
     <row r="9">
@@ -971,19 +971,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>103776.8</v>
+        <v>53924.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.374953131799474</v>
+        <v>0.786333150608707</v>
       </c>
       <c r="E9" t="n">
-        <v>2.018710162029553</v>
+        <v>0.668383178017401</v>
       </c>
       <c r="F9" t="n">
-        <v>1.638430453720926</v>
+        <v>0.5424747812818772</v>
       </c>
     </row>
     <row r="10">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20.75605246448776</v>
+        <v>14.17257997498331</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34.27033383155648</v>
+        <v>32.88568676563081</v>
       </c>
       <c r="F11" t="n">
-        <v>27.09827418311721</v>
+        <v>26.00340460805774</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47.85432664760496</v>
+        <v>40.17598458304104</v>
       </c>
     </row>
     <row r="13">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
   </sheetData>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.52201661875056</v>
+        <v>28.90956478519214</v>
       </c>
       <c r="C2" t="n">
-        <v>35.00349174971859</v>
+        <v>33.39103991616017</v>
       </c>
       <c r="D2" t="n">
-        <v>39.48496688068662</v>
+        <v>37.8725150471282</v>
       </c>
       <c r="E2" t="n">
-        <v>43.96644201165465</v>
+        <v>42.35399017809623</v>
       </c>
       <c r="F2" t="n">
-        <v>48.44791714262269</v>
+        <v>46.83546530906425</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.79578577132481</v>
+        <v>29.83780854486101</v>
       </c>
       <c r="C3" t="n">
-        <v>36.27726090229283</v>
+        <v>34.31928367582903</v>
       </c>
       <c r="D3" t="n">
-        <v>40.75873603326087</v>
+        <v>38.80075880679706</v>
       </c>
       <c r="E3" t="n">
-        <v>45.2402111642289</v>
+        <v>43.28223393776509</v>
       </c>
       <c r="F3" t="n">
-        <v>49.72168629519692</v>
+        <v>47.76370906873312</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.06955492389905</v>
+        <v>30.76605230452988</v>
       </c>
       <c r="C4" t="n">
-        <v>37.55103005486708</v>
+        <v>35.2475274354979</v>
       </c>
       <c r="D4" t="n">
-        <v>42.03250518583511</v>
+        <v>39.72900256646593</v>
       </c>
       <c r="E4" t="n">
-        <v>46.51398031680313</v>
+        <v>44.21047769743396</v>
       </c>
       <c r="F4" t="n">
-        <v>50.99545544777116</v>
+        <v>48.69195282840199</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34.34332407647329</v>
+        <v>31.69429606419874</v>
       </c>
       <c r="C5" t="n">
-        <v>38.82479920744132</v>
+        <v>36.17577119516676</v>
       </c>
       <c r="D5" t="n">
-        <v>43.30627433840935</v>
+        <v>40.6572463261348</v>
       </c>
       <c r="E5" t="n">
-        <v>47.78774946937737</v>
+        <v>45.13872145710283</v>
       </c>
       <c r="F5" t="n">
-        <v>52.26922460034541</v>
+        <v>49.62019658807085</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35.61709322904753</v>
+        <v>32.6225398238676</v>
       </c>
       <c r="C6" t="n">
-        <v>40.09856836001556</v>
+        <v>37.10401495483563</v>
       </c>
       <c r="D6" t="n">
-        <v>44.5800434909836</v>
+        <v>41.58549008580366</v>
       </c>
       <c r="E6" t="n">
-        <v>49.06151862195162</v>
+        <v>46.06696521677169</v>
       </c>
       <c r="F6" t="n">
-        <v>53.54299375291966</v>
+        <v>50.54844034773972</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>41.99</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>42.12</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>42.16</v>
+        <v>39.84</v>
       </c>
     </row>
   </sheetData>
@@ -1274,7 +1274,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.86</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>530103.5142182048</v>
+        <v>549196.7047767208</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.576269250885495</v>
+        <v>4.741096644990014</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.88</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>549196.7047767208</v>
+        <v>500714.9758095087</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.741096644990014</v>
+        <v>4.322564340352072</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.29</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500714.9758095087</v>
+        <v>589629.3436065195</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.322564340352072</v>
+        <v>5.090142891328995</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/eco_fv_report.xlsx
+++ b/outputs/eco_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.04000000000001</v>
+        <v>66.86</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>589629.3436065195</v>
+        <v>623697.5855834794</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.090142891328995</v>
+        <v>5.384246672966468</v>
       </c>
     </row>
   </sheetData>
